--- a/testbuild/StructureDefinition-no-basis-partof.xlsx
+++ b/testbuild/StructureDefinition-no-basis-partof.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.3-test</t>
+    <t>2.2.4-test</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-06T10:34:36+00:00</t>
+    <t>2026-10-04T17:32:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/StructureDefinition-no-basis-partof.xlsx
+++ b/testbuild/StructureDefinition-no-basis-partof.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-04T17:32:19+00:00</t>
+    <t>2026-10-04T17:44:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
